--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.2406846115995</v>
+        <v>8.164111249384918</v>
       </c>
       <c r="D2" t="n">
-        <v>13.93971552180229</v>
+        <v>2.265203772292872</v>
       </c>
       <c r="E2" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F2" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.56633819857014</v>
+        <v>9.517029957267649</v>
       </c>
       <c r="D3" t="n">
-        <v>20.52639164542688</v>
+        <v>3.335538642381868</v>
       </c>
       <c r="E3" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F3" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.28000230559245</v>
+        <v>4.595500374658774</v>
       </c>
       <c r="D4" t="n">
-        <v>14.46594423563498</v>
+        <v>2.350715938290685</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.69195230057068</v>
+        <v>7.262442248842735</v>
       </c>
       <c r="D5" t="n">
-        <v>43.63317702090847</v>
+        <v>7.090391265897627</v>
       </c>
       <c r="E5" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.55903877308661</v>
+        <v>4.315843800626573</v>
       </c>
       <c r="D6" t="n">
-        <v>20.7177235463815</v>
+        <v>3.366630076286993</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.05808795764227</v>
+        <v>8.78443929311687</v>
       </c>
       <c r="D7" t="n">
-        <v>52.70165423013448</v>
+        <v>8.564018812396853</v>
       </c>
       <c r="E7" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.25625292176914</v>
+        <v>4.429141099787484</v>
       </c>
       <c r="D8" t="n">
-        <v>25.89998038685682</v>
+        <v>4.208746812864233</v>
       </c>
       <c r="E8" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F8" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.209445902409</v>
+        <v>3.446534959141463</v>
       </c>
       <c r="D9" t="n">
-        <v>22.62421749767043</v>
+        <v>3.676435343371446</v>
       </c>
       <c r="E9" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F9" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.861377991341032</v>
+        <v>1.602473923592918</v>
       </c>
       <c r="D10" t="n">
-        <v>8.422147916814435</v>
+        <v>1.368599036482346</v>
       </c>
       <c r="E10" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F10" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.39082174180407</v>
+        <v>5.913508533043161</v>
       </c>
       <c r="D11" t="n">
-        <v>18.80204744336219</v>
+        <v>3.055332709546356</v>
       </c>
       <c r="E11" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F11" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.65062037018003</v>
+        <v>1.730725810154255</v>
       </c>
       <c r="D12" t="n">
-        <v>10.79326958432519</v>
+        <v>1.753906307452843</v>
       </c>
       <c r="E12" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F12" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.16471767535324</v>
+        <v>4.089266622244902</v>
       </c>
       <c r="D13" t="n">
-        <v>23.83907073285081</v>
+        <v>3.873848994088257</v>
       </c>
       <c r="E13" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F13" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.84948638508649</v>
+        <v>3.875541537576554</v>
       </c>
       <c r="D14" t="n">
-        <v>24.40509251294912</v>
+        <v>3.965827533354232</v>
       </c>
       <c r="E14" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F14" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.42010264458553</v>
+        <v>5.59326667974515</v>
       </c>
       <c r="D15" t="n">
-        <v>33.35026437270539</v>
+        <v>5.419417960564626</v>
       </c>
       <c r="E15" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F15" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>50.47857325316149</v>
+        <v>8.202768153638743</v>
       </c>
       <c r="D16" t="n">
-        <v>7.230638946704095</v>
+        <v>1.174978828839415</v>
       </c>
       <c r="E16" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F16" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.17099733931435</v>
+        <v>7.177787067638581</v>
       </c>
       <c r="D17" t="n">
-        <v>42.8846272395577</v>
+        <v>6.968751926428126</v>
       </c>
       <c r="E17" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F17" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.72872240014875</v>
+        <v>9.218417390024172</v>
       </c>
       <c r="D18" t="n">
-        <v>55.3694116358525</v>
+        <v>8.997529390826031</v>
       </c>
       <c r="E18" t="n">
-        <v>15.05281311705132</v>
+        <v>2.44608213152084</v>
       </c>
       <c r="F18" t="n">
-        <v>14.3988179431854</v>
+        <v>2.339807915767627</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
